--- a/data/trans_orig/P15B_3_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P15B_3_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2007</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2007 (tasa de respuesta: 51,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15129</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17595</t>
+          <t>17553</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15867</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>21814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33451</t>
+          <t>33113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>85,68%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9184</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22201</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26356</t>
+          <t>25615</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>20378</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33596</t>
+          <t>33521</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23477</t>
+          <t>22463</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46559</t>
+          <t>47300</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62527</t>
+          <t>62633</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15818</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>10995</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11248</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24719</t>
+          <t>24461</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,05%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21232</t>
+          <t>22092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23201</t>
+          <t>23459</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36672</t>
+          <t>36561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>7974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25941</t>
+          <t>25736</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32812</t>
+          <t>32811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19309</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47820</t>
+          <t>47819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55659</t>
+          <t>55615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29670</t>
+          <t>30208</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51103</t>
+          <t>50354</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17783</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37066</t>
+          <t>36767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63918</t>
+          <t>62093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71974</t>
+          <t>72723</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93407</t>
+          <t>92869</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76023</t>
+          <t>76731</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>88843</t>
+          <t>89103</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152965</t>
+          <t>154790</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>179817</t>
+          <t>180116</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2012</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2012 (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22257</t>
+          <t>21888</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10826</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26779</t>
+          <t>26460</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36765</t>
+          <t>37134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50220</t>
+          <t>49808</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43999</t>
+          <t>43056</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84719</t>
+          <t>85038</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100672</t>
+          <t>100171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25005</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12111</t>
+          <t>12809</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28976</t>
+          <t>29525</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56284</t>
+          <t>56859</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70923</t>
+          <t>71178</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65711</t>
+          <t>66039</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73665</t>
+          <t>73656</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126937</t>
+          <t>126388</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143802</t>
+          <t>143104</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>8608</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21017</t>
+          <t>21535</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12909</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28600</t>
+          <t>28686</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37391</t>
+          <t>36873</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49628</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44136</t>
+          <t>44166</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55089</t>
+          <t>55739</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86853</t>
+          <t>86767</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102765</t>
+          <t>103019</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23810</t>
+          <t>24380</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29245</t>
+          <t>29583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64442</t>
+          <t>63872</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78052</t>
+          <t>78716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64312</t>
+          <t>63279</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>130269</t>
+          <t>129931</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>148211</t>
+          <t>147598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>48742</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77841</t>
+          <t>76648</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23649</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60244</t>
+          <t>59450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94567</t>
+          <t>94118</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209131</t>
+          <t>210324</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>237476</t>
+          <t>238230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>231756</t>
+          <t>232272</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>248464</t>
+          <t>248844</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>447810</t>
+          <t>448259</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>482133</t>
+          <t>482927</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2016</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2016 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10668</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>854</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13921</t>
+          <t>14448</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29901</t>
+          <t>29075</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37818</t>
+          <t>37774</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40954</t>
+          <t>40456</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47834</t>
+          <t>47821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74497</t>
+          <t>73970</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85419</t>
+          <t>84740</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18547</t>
+          <t>19785</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41928</t>
+          <t>40690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54384</t>
+          <t>53873</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46535</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48599</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>89383</t>
+          <t>89105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102993</t>
+          <t>103021</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>18720</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24001</t>
+          <t>24021</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34506</t>
+          <t>34519</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21018</t>
+          <t>21141</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29606</t>
+          <t>29660</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49559</t>
+          <t>49507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62385</t>
+          <t>62496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>20733</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47702</t>
+          <t>47972</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57893</t>
+          <t>57958</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50047</t>
+          <t>50571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59672</t>
+          <t>60389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102626</t>
+          <t>102771</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115736</t>
+          <t>116386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>20451</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>40329</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22882</t>
+          <t>21957</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31716</t>
+          <t>31690</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56626</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157265</t>
+          <t>157440</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177556</t>
+          <t>177318</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>168571</t>
+          <t>169496</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>183307</t>
+          <t>183533</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>332597</t>
+          <t>331998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>357507</t>
+          <t>357533</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2023</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22541</t>
+          <t>23077</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27220</t>
+          <t>26902</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22340</t>
+          <t>21804</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36717</t>
+          <t>36730</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37756</t>
+          <t>37560</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42282</t>
+          <t>42225</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60903</t>
+          <t>61221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78198</t>
+          <t>78109</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,64%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22787</t>
+          <t>23881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11134</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29586</t>
+          <t>29415</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43342</t>
+          <t>42248</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58474</t>
+          <t>57444</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46101</t>
+          <t>46097</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55912</t>
+          <t>55875</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93778</t>
+          <t>93949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>111620</t>
+          <t>111788</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13010</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>470</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15407</t>
+          <t>15366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26327</t>
+          <t>26216</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39791</t>
+          <t>39858</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43643</t>
+          <t>43638</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57935</t>
+          <t>57976</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69340</t>
+          <t>69190</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18639</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27032</t>
+          <t>26159</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40246</t>
+          <t>41808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53829</t>
+          <t>53433</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55525</t>
+          <t>55852</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65166</t>
+          <t>65435</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100871</t>
+          <t>101744</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116931</t>
+          <t>117218</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33598</t>
+          <t>34267</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60830</t>
+          <t>61139</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25071</t>
+          <t>24561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49842</t>
+          <t>47614</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81321</t>
+          <t>78884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>138300</t>
+          <t>137991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165532</t>
+          <t>164863</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188532</t>
+          <t>189042</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203530</t>
+          <t>203576</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>331412</t>
+          <t>333849</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>362891</t>
+          <t>365119</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,46%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15B_3_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P15B_3_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>15577</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>22110</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33113</t>
+          <t>33553</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22402</t>
+          <t>21734</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7672</t>
+          <t>7529</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>9994</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25615</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20378</t>
+          <t>21046</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33521</t>
+          <t>34161</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22463</t>
+          <t>22606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47300</t>
+          <t>47629</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62633</t>
+          <t>62921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>11843</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11359</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24461</t>
+          <t>24495</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17652</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22092</t>
+          <t>21282</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23459</t>
+          <t>23425</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36561</t>
+          <t>36746</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,68%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>9437</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25736</t>
+          <t>25524</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32811</t>
+          <t>32820</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19335</t>
+          <t>18271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47819</t>
+          <t>47962</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55615</t>
+          <t>55706</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>29880</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50354</t>
+          <t>51811</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36767</t>
+          <t>37616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62093</t>
+          <t>62717</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72723</t>
+          <t>71266</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92869</t>
+          <t>93197</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76731</t>
+          <t>76808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89103</t>
+          <t>89342</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>154790</t>
+          <t>154166</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>180116</t>
+          <t>179267</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,66%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9583</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21888</t>
+          <t>22774</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11327</t>
+          <t>10947</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26460</t>
+          <t>26509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37134</t>
+          <t>36248</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49808</t>
+          <t>49439</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43056</t>
+          <t>43990</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85038</t>
+          <t>84989</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100171</t>
+          <t>100551</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10111</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24430</t>
+          <t>24990</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>12880</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29525</t>
+          <t>29174</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56859</t>
+          <t>56299</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71178</t>
+          <t>71332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66039</t>
+          <t>65931</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73656</t>
+          <t>73660</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126388</t>
+          <t>126739</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143104</t>
+          <t>143033</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,74%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21535</t>
+          <t>21234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12879</t>
+          <t>12844</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28686</t>
+          <t>28624</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36873</t>
+          <t>37174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>49884</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44166</t>
+          <t>44201</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55739</t>
+          <t>55323</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86767</t>
+          <t>86829</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103019</t>
+          <t>103674</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>10265</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24380</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29583</t>
+          <t>28689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63872</t>
+          <t>63447</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78716</t>
+          <t>77987</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63279</t>
+          <t>63967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129931</t>
+          <t>130825</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147598</t>
+          <t>148029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48742</t>
+          <t>48908</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76648</t>
+          <t>76630</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>23025</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59450</t>
+          <t>60449</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94118</t>
+          <t>92848</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>210324</t>
+          <t>210342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>238230</t>
+          <t>238064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>232272</t>
+          <t>232380</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>248844</t>
+          <t>248400</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>448259</t>
+          <t>449529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>482927</t>
+          <t>481928</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>10062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>813</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14448</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29075</t>
+          <t>29681</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37774</t>
+          <t>37786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40456</t>
+          <t>40949</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47821</t>
+          <t>47862</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73970</t>
+          <t>73852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84740</t>
+          <t>84596</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19785</t>
+          <t>18625</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19969</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40690</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53873</t>
+          <t>54081</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>89105</t>
+          <t>89884</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>103021</t>
+          <t>103014</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10420</t>
+          <t>10541</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18720</t>
+          <t>19748</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24021</t>
+          <t>24532</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34519</t>
+          <t>34627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21141</t>
+          <t>21020</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29660</t>
+          <t>29623</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49507</t>
+          <t>48479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62496</t>
+          <t>62353</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20733</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47972</t>
+          <t>47556</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57958</t>
+          <t>57949</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50571</t>
+          <t>50014</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60389</t>
+          <t>60557</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102771</t>
+          <t>102081</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116386</t>
+          <t>116541</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20451</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40329</t>
+          <t>40235</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21957</t>
+          <t>22800</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31690</t>
+          <t>32791</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57225</t>
+          <t>58691</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157440</t>
+          <t>157534</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177318</t>
+          <t>177725</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169496</t>
+          <t>168653</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>183533</t>
+          <t>183351</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>331998</t>
+          <t>330532</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>357533</t>
+          <t>356432</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14270</t>
+          <t>15107</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>8079</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23077</t>
+          <t>25555</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16831</t>
+          <t>17781</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26902</t>
+          <t>30300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30611</t>
+          <t>34584</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21804</t>
+          <t>24136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36730</t>
+          <t>41612</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>44247</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37560</t>
+          <t>40940</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42225</t>
+          <t>45902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>71292</t>
+          <t>78831</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61221</t>
+          <t>66312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78109</t>
+          <t>85990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>88123</t>
+          <t>96612</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88123</t>
+          <t>96612</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88123</t>
+          <t>96612</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15092</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8685</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23881</t>
+          <t>27155</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,17 +6947,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11138</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>21469</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11576</t>
+          <t>13295</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29415</t>
+          <t>32471</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>56853</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42248</t>
+          <t>46547</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57444</t>
+          <t>64064</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,17 +7060,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>53021</t>
+          <t>58184</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46097</t>
+          <t>50701</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55875</t>
+          <t>61505</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>104058</t>
+          <t>115037</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93949</t>
+          <t>104035</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>111788</t>
+          <t>123211</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,26%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66129</t>
+          <t>73702</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66129</t>
+          <t>73702</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66129</t>
+          <t>73702</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57235</t>
+          <t>62804</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57235</t>
+          <t>62804</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57235</t>
+          <t>62804</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>123364</t>
+          <t>136506</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>123364</t>
+          <t>136506</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>123364</t>
+          <t>136506</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>13161</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>449</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15366</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22328</t>
+          <t>25961</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>19811</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26216</t>
+          <t>30261</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42495</t>
+          <t>47815</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39858</t>
+          <t>45018</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43638</t>
+          <t>49032</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>64823</t>
+          <t>73775</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57976</t>
+          <t>66908</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69190</t>
+          <t>78728</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44108</t>
+          <t>49481</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44108</t>
+          <t>49481</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44108</t>
+          <t>49481</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>82452</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>82452</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>82452</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10540</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17077</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13166</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17603</t>
+          <t>18149</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>11589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26159</t>
+          <t>26853</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>48666</t>
+          <t>53006</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41808</t>
+          <t>44926</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53433</t>
+          <t>58137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>61635</t>
+          <t>65364</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55852</t>
+          <t>59161</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65435</t>
+          <t>68972</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>110300</t>
+          <t>118371</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>101744</t>
+          <t>109667</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>117218</t>
+          <t>124931</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>69018</t>
+          <t>72973</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69018</t>
+          <t>72973</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69018</t>
+          <t>72973</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>127903</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>127903</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>127903</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>46487</t>
+          <t>49506</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34267</t>
+          <t>37246</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61139</t>
+          <t>66343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24561</t>
+          <t>26274</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>62259</t>
+          <t>66076</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47614</t>
+          <t>52043</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78884</t>
+          <t>84630</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>152643</t>
+          <t>170405</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137991</t>
+          <t>153568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164863</t>
+          <t>182665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>197831</t>
+          <t>215610</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>189042</t>
+          <t>205906</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203576</t>
+          <t>221520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>350474</t>
+          <t>386015</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>333849</t>
+          <t>367461</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>365119</t>
+          <t>400048</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
